--- a/嘉宾名单.xlsx
+++ b/嘉宾名单.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,10 +452,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>是否VIP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>英文名</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>别名</t>
         </is>
@@ -482,10 +487,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Ethan Zhao</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Ethan,阿赵</t>
         </is>
@@ -512,10 +522,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Noah Qian</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -536,8 +551,13 @@
           <t>是</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -560,10 +580,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Ryan Li</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -586,10 +611,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Mason Zhou</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Mason,阿周</t>
         </is>
@@ -616,10 +646,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Aiden Wu</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Aiden,阿吴</t>
         </is>
@@ -644,8 +679,13 @@
           <t>是</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -666,8 +706,13 @@
           <t>是</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -690,10 +735,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Jason Feng</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Jason,阿冯</t>
         </is>
@@ -718,8 +768,13 @@
           <t>是</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -742,10 +797,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Iris Lin</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -768,10 +828,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Chloe He</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Chloe,小何</t>
         </is>
@@ -796,8 +861,13 @@
           <t>是</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -818,8 +888,13 @@
           <t>是</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -842,10 +917,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Mia Xie</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Mia,小谢</t>
         </is>
@@ -872,10 +952,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Luna Song</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Luna,小宋</t>
         </is>
@@ -902,10 +987,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Nina Tang</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Nina,小唐</t>
         </is>
@@ -932,10 +1022,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Anna Han</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -956,8 +1051,13 @@
           <t>是</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -978,8 +1078,13 @@
           <t>是</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
